--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32412,7 +32412,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1233" t="n">
-        <v>3281263</v>
+        <v>3395000</v>
       </c>
       <c r="C1233" t="n">
         <v>48.2900009155273</v>
@@ -32430,6 +32430,32 @@
         <v>46.9900016784668</v>
       </c>
       <c r="H1233" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1234" t="n">
+        <v>3353279</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>49.4900016784668</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>47.6300010681152</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>48.3300018310547</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="H1234" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32438,7 +32438,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1234" t="n">
-        <v>3353279</v>
+        <v>3353900</v>
       </c>
       <c r="C1234" t="n">
         <v>49.4900016784668</v>
@@ -32447,7 +32447,7 @@
         <v>47.6300010681152</v>
       </c>
       <c r="E1234" t="n">
-        <v>48.3300018310547</v>
+        <v>48.3349990844727</v>
       </c>
       <c r="F1234" t="n">
         <v>49.25</v>
@@ -32456,6 +32456,32 @@
         <v>49.25</v>
       </c>
       <c r="H1234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1235" t="n">
+        <v>3220732</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>50.2299995422363</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>48.4300003051758</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>48.4949989318848</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="H1235" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32464,7 +32464,7 @@
         <v>46280.5625</v>
       </c>
       <c r="B1235" t="n">
-        <v>3220732</v>
+        <v>3520400</v>
       </c>
       <c r="C1235" t="n">
         <v>50.2299995422363</v>
@@ -32482,6 +32482,32 @@
         <v>49.0999984741211</v>
       </c>
       <c r="H1235" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1236" t="n">
+        <v>3116885</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>49.310001373291</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>48.060001373291</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>48.060001373291</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>48.7700004577637</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>48.7700004577637</v>
+      </c>
+      <c r="H1236" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32490,7 +32490,7 @@
         <v>46281.5625</v>
       </c>
       <c r="B1236" t="n">
-        <v>3116885</v>
+        <v>3120600</v>
       </c>
       <c r="C1236" t="n">
         <v>49.310001373291</v>
@@ -32508,6 +32508,32 @@
         <v>48.7700004577637</v>
       </c>
       <c r="H1236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1237" t="n">
+        <v>3894205</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>50.4700012207031</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>48.0778007507324</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>48.2599983215332</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>50.2700004577637</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>50.2700004577637</v>
+      </c>
+      <c r="H1237" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32516,16 +32516,16 @@
         <v>46282.5625</v>
       </c>
       <c r="B1237" t="n">
-        <v>3894205</v>
+        <v>3973000</v>
       </c>
       <c r="C1237" t="n">
         <v>50.4700012207031</v>
       </c>
       <c r="D1237" t="n">
-        <v>48.0778007507324</v>
+        <v>48.0699996948242</v>
       </c>
       <c r="E1237" t="n">
-        <v>48.2599983215332</v>
+        <v>48.5400009155273</v>
       </c>
       <c r="F1237" t="n">
         <v>50.2700004577637</v>
@@ -32534,6 +32534,32 @@
         <v>50.2700004577637</v>
       </c>
       <c r="H1237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>5892302</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>50.6699981689453</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>49.064998626709</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>50.6699981689453</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>49.2299995422363</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>49.2299995422363</v>
+      </c>
+      <c r="H1238" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32542,7 +32542,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1238" t="n">
-        <v>5892302</v>
+        <v>5948900</v>
       </c>
       <c r="C1238" t="n">
         <v>50.6699981689453</v>
@@ -32560,6 +32560,32 @@
         <v>49.2299995422363</v>
       </c>
       <c r="H1238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1239" t="n">
+        <v>2240495</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>50.1399993896484</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>49.3800010681152</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>49.7900009155273</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>49.7900009155273</v>
+      </c>
+      <c r="H1239" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32568,10 +32568,10 @@
         <v>46286.5625</v>
       </c>
       <c r="B1239" t="n">
-        <v>2240495</v>
+        <v>2424100</v>
       </c>
       <c r="C1239" t="n">
-        <v>50.1399993896484</v>
+        <v>50.1599998474121</v>
       </c>
       <c r="D1239" t="n">
         <v>49.0999984741211</v>
@@ -32586,6 +32586,32 @@
         <v>49.7900009155273</v>
       </c>
       <c r="H1239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1240" t="n">
+        <v>2944800</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>50.6679992675781</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>48.0449981689453</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>50.4900016784668</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>48.8199996948242</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>48.8199996948242</v>
+      </c>
+      <c r="H1240" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -28874,7 +28874,7 @@
         <v>46288.5625</v>
       </c>
       <c r="B1240" t="n">
-        <v>3677337</v>
+        <v>3741700</v>
       </c>
       <c r="C1240" t="n">
         <v>49.7999992370605</v>
@@ -28889,6 +28889,29 @@
         <v>49.0099983215332</v>
       </c>
       <c r="G1240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1241" t="n">
+        <v>6135948</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>49.2400016784668</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>48.0050010681152</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>48.8899993896484</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>48.6199989318848</v>
+      </c>
+      <c r="G1241" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32672,16 +32672,16 @@
         <v>46290.5625</v>
       </c>
       <c r="B1243" t="n">
-        <v>3831449</v>
+        <v>3898400</v>
       </c>
       <c r="C1243" t="n">
         <v>48.6100006103516</v>
       </c>
       <c r="D1243" t="n">
-        <v>46.810001373291</v>
+        <v>46.8050003051758</v>
       </c>
       <c r="E1243" t="n">
-        <v>48.5999984741211</v>
+        <v>48.6100006103516</v>
       </c>
       <c r="F1243" t="n">
         <v>46.8450012207031</v>
@@ -32690,6 +32690,32 @@
         <v>46.8450012207031</v>
       </c>
       <c r="H1243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>5194380</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>46.4700012207031</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>44.2200012207031</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>45.5289993286133</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>46.2099990844727</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>46.2099990844727</v>
+      </c>
+      <c r="H1244" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32698,7 +32698,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1244" t="n">
-        <v>5194380</v>
+        <v>5206200</v>
       </c>
       <c r="C1244" t="n">
         <v>46.4700012207031</v>
@@ -32707,7 +32707,7 @@
         <v>44.2200012207031</v>
       </c>
       <c r="E1244" t="n">
-        <v>45.5289993286133</v>
+        <v>45.6349983215332</v>
       </c>
       <c r="F1244" t="n">
         <v>46.2099990844727</v>
@@ -32716,6 +32716,32 @@
         <v>46.2099990844727</v>
       </c>
       <c r="H1244" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1245" t="n">
+        <v>4200198</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>47.0999984741211</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>45.5200004577637</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>46</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>46.7099990844727</v>
+      </c>
+      <c r="G1245" t="n">
+        <v>46.7099990844727</v>
+      </c>
+      <c r="H1245" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32724,13 +32724,13 @@
         <v>46294.5625</v>
       </c>
       <c r="B1245" t="n">
-        <v>4200198</v>
+        <v>4200400</v>
       </c>
       <c r="C1245" t="n">
         <v>47.0999984741211</v>
       </c>
       <c r="D1245" t="n">
-        <v>45.5200004577637</v>
+        <v>45.5099983215332</v>
       </c>
       <c r="E1245" t="n">
         <v>46</v>
@@ -32742,6 +32742,32 @@
         <v>46.7099990844727</v>
       </c>
       <c r="H1245" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>3498070</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>48.0999984741211</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>46.4799995422363</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>46.6199989318848</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="G1246" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="H1246" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32750,16 +32750,16 @@
         <v>46295.5625</v>
       </c>
       <c r="B1246" t="n">
-        <v>3498070</v>
+        <v>3550800</v>
       </c>
       <c r="C1246" t="n">
-        <v>48.0999984741211</v>
+        <v>48.1100006103516</v>
       </c>
       <c r="D1246" t="n">
         <v>46.4799995422363</v>
       </c>
       <c r="E1246" t="n">
-        <v>46.6199989318848</v>
+        <v>46.5800018310547</v>
       </c>
       <c r="F1246" t="n">
         <v>47.25</v>
@@ -32768,6 +32768,32 @@
         <v>47.25</v>
       </c>
       <c r="H1246" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1247" t="n">
+        <v>4601614</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>50</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>47.3400001525879</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>48.1800003051758</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>49.9500007629395</v>
+      </c>
+      <c r="G1247" t="n">
+        <v>49.9500007629395</v>
+      </c>
+      <c r="H1247" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32776,7 +32776,7 @@
         <v>46296.5625</v>
       </c>
       <c r="B1247" t="n">
-        <v>4601614</v>
+        <v>4602400</v>
       </c>
       <c r="C1247" t="n">
         <v>50</v>
@@ -32794,6 +32794,32 @@
         <v>49.9500007629395</v>
       </c>
       <c r="H1247" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>2984378</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>49</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>50.7700004577637</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>49.7799987792969</v>
+      </c>
+      <c r="G1248" t="n">
+        <v>49.7799987792969</v>
+      </c>
+      <c r="H1248" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32802,7 +32802,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1248" t="n">
-        <v>2984378</v>
+        <v>2984500</v>
       </c>
       <c r="C1248" t="n">
         <v>51.25</v>
@@ -32811,7 +32811,7 @@
         <v>49</v>
       </c>
       <c r="E1248" t="n">
-        <v>50.7700004577637</v>
+        <v>50.8499984741211</v>
       </c>
       <c r="F1248" t="n">
         <v>49.7799987792969</v>
@@ -32820,6 +32820,32 @@
         <v>49.7799987792969</v>
       </c>
       <c r="H1248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>3208565</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>51.7599983215332</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>49.689998626709</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>49.8499984741211</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H1249" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32828,7 +32828,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1249" t="n">
-        <v>3208565</v>
+        <v>3211300</v>
       </c>
       <c r="C1249" t="n">
         <v>51.7599983215332</v>
@@ -32846,6 +32846,32 @@
         <v>51.5</v>
       </c>
       <c r="H1249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>4256118</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>53.3800010681152</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>50.8600006103516</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>52.0349998474121</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>51.6300010681152</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>51.6300010681152</v>
+      </c>
+      <c r="H1250" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32854,16 +32854,16 @@
         <v>46301.5625</v>
       </c>
       <c r="B1250" t="n">
-        <v>4256118</v>
+        <v>4256500</v>
       </c>
       <c r="C1250" t="n">
         <v>53.3800010681152</v>
       </c>
       <c r="D1250" t="n">
-        <v>50.8600006103516</v>
+        <v>50.8499984741211</v>
       </c>
       <c r="E1250" t="n">
-        <v>52.0349998474121</v>
+        <v>51.9500007629395</v>
       </c>
       <c r="F1250" t="n">
         <v>51.6300010681152</v>
@@ -32872,6 +32872,32 @@
         <v>51.6300010681152</v>
       </c>
       <c r="H1250" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1251" t="n">
+        <v>2403535</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>52.5299987792969</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>51.3199996948242</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>51.6100006103516</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>51.9900016784668</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>51.9900016784668</v>
+      </c>
+      <c r="H1251" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32880,7 +32880,7 @@
         <v>46302.5625</v>
       </c>
       <c r="B1251" t="n">
-        <v>2403535</v>
+        <v>2404400</v>
       </c>
       <c r="C1251" t="n">
         <v>52.5299987792969</v>
@@ -32898,6 +32898,32 @@
         <v>51.9900016784668</v>
       </c>
       <c r="H1251" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1252" t="n">
+        <v>4716893</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>53.6199989318848</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>51.6200981140137</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>52.0299987792969</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>53.560001373291</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>53.560001373291</v>
+      </c>
+      <c r="H1252" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32906,13 +32906,13 @@
         <v>46303.5625</v>
       </c>
       <c r="B1252" t="n">
-        <v>4716893</v>
+        <v>4724300</v>
       </c>
       <c r="C1252" t="n">
         <v>53.6199989318848</v>
       </c>
       <c r="D1252" t="n">
-        <v>51.6200981140137</v>
+        <v>51.6199989318848</v>
       </c>
       <c r="E1252" t="n">
         <v>52.0299987792969</v>
@@ -32924,6 +32924,32 @@
         <v>53.560001373291</v>
       </c>
       <c r="H1252" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1253" t="n">
+        <v>2370535</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>55.1100006103516</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>53.8800010681152</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>53.9300003051758</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>55.0900001525879</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>55.0900001525879</v>
+      </c>
+      <c r="H1253" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32932,7 +32932,7 @@
         <v>46304.5625</v>
       </c>
       <c r="B1253" t="n">
-        <v>2370535</v>
+        <v>2370800</v>
       </c>
       <c r="C1253" t="n">
         <v>55.1100006103516</v>
@@ -32941,7 +32941,7 @@
         <v>53.8800010681152</v>
       </c>
       <c r="E1253" t="n">
-        <v>53.9300003051758</v>
+        <v>54.0499992370605</v>
       </c>
       <c r="F1253" t="n">
         <v>55.0900001525879</v>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -32984,7 +32984,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1255" t="n">
-        <v>9356692</v>
+        <v>9564500</v>
       </c>
       <c r="C1255" t="n">
         <v>57.8899993896484</v>
@@ -32993,7 +32993,7 @@
         <v>51.6100006103516</v>
       </c>
       <c r="E1255" t="n">
-        <v>55.9900016784668</v>
+        <v>56</v>
       </c>
       <c r="F1255" t="n">
         <v>51.9500007629395</v>
@@ -33002,6 +33002,32 @@
         <v>51.9500007629395</v>
       </c>
       <c r="H1255" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1256" t="n">
+        <v>6135784</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>54.9300003051758</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>50.3650016784668</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>50.4000015258789</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>53.1599998474121</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>53.1599998474121</v>
+      </c>
+      <c r="H1256" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -33010,16 +33010,16 @@
         <v>46309.5625</v>
       </c>
       <c r="B1256" t="n">
-        <v>6135784</v>
+        <v>6160200</v>
       </c>
       <c r="C1256" t="n">
-        <v>54.9300003051758</v>
+        <v>54.9589996337891</v>
       </c>
       <c r="D1256" t="n">
-        <v>50.3650016784668</v>
+        <v>50.2999992370605</v>
       </c>
       <c r="E1256" t="n">
-        <v>50.4000015258789</v>
+        <v>50.5099983215332</v>
       </c>
       <c r="F1256" t="n">
         <v>53.1599998474121</v>
@@ -33028,6 +33028,32 @@
         <v>53.1599998474121</v>
       </c>
       <c r="H1256" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1257" t="n">
+        <v>4478439</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>56.0299987792969</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>52.2000007629395</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>52.2150001525879</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>55.939998626709</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>55.939998626709</v>
+      </c>
+      <c r="H1257" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -33036,7 +33036,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1257" t="n">
-        <v>4478439</v>
+        <v>4503800</v>
       </c>
       <c r="C1257" t="n">
         <v>56.0299987792969</v>
@@ -33054,6 +33054,32 @@
         <v>55.939998626709</v>
       </c>
       <c r="H1257" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1258" t="n">
+        <v>3372493</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>57.2219009399414</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>52.2099990844727</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>56.1800003051758</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>52.7599983215332</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>52.7599983215332</v>
+      </c>
+      <c r="H1258" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -36868,7 +36868,7 @@
         <v>46314.5625</v>
       </c>
       <c r="C1259" t="n">
-        <v>53.0400009155273</v>
+        <v>52.7949981689453</v>
       </c>
       <c r="D1259" t="n">
         <v>53.7150001525879</v>
@@ -36883,9 +36883,38 @@
         <v>53.2900009155273</v>
       </c>
       <c r="H1259" t="n">
-        <v>2652733</v>
+        <v>2652800</v>
       </c>
       <c r="I1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1260" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>53.0299987792969</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>55.7299003601074</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>53.0299987792969</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>55</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>55</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>2420558</v>
+      </c>
+      <c r="I1260" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -36900,7 +36900,7 @@
         <v>53.0299987792969</v>
       </c>
       <c r="D1260" t="n">
-        <v>55.7299003601074</v>
+        <v>55.7299995422363</v>
       </c>
       <c r="E1260" t="n">
         <v>53.0299987792969</v>
@@ -36912,9 +36912,38 @@
         <v>55</v>
       </c>
       <c r="H1260" t="n">
-        <v>2420558</v>
+        <v>2563100</v>
       </c>
       <c r="I1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1261" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>55</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>56.189998626709</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>54.7663993835449</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>55.4500007629395</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>55.4500007629395</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>2249074</v>
+      </c>
+      <c r="I1261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -36926,13 +36926,13 @@
         <v>46316.5625</v>
       </c>
       <c r="C1261" t="n">
-        <v>55</v>
+        <v>54.939998626709</v>
       </c>
       <c r="D1261" t="n">
-        <v>56.189998626709</v>
+        <v>56.2000007629395</v>
       </c>
       <c r="E1261" t="n">
-        <v>54.7663993835449</v>
+        <v>54.765998840332</v>
       </c>
       <c r="F1261" t="n">
         <v>55.4500007629395</v>
@@ -36941,9 +36941,38 @@
         <v>55.4500007629395</v>
       </c>
       <c r="H1261" t="n">
-        <v>2249074</v>
+        <v>2250300</v>
       </c>
       <c r="I1261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1262" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>55.9000015258789</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>56.6500015258789</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>54.0400009155273</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>54.5299987792969</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>54.5299987792969</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>4162279</v>
+      </c>
+      <c r="I1262" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -36970,9 +36970,38 @@
         <v>54.5299987792969</v>
       </c>
       <c r="H1262" t="n">
-        <v>4162279</v>
+        <v>4316300</v>
       </c>
       <c r="I1262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1263" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>54.3600006103516</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>57.1349983215332</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>54.0250015258789</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>56.2799987792969</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>56.2799987792969</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>3316954</v>
+      </c>
+      <c r="I1263" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -36984,7 +36984,7 @@
         <v>46318.5625</v>
       </c>
       <c r="C1263" t="n">
-        <v>54.3600006103516</v>
+        <v>54.3499984741211</v>
       </c>
       <c r="D1263" t="n">
         <v>57.1349983215332</v>
@@ -36999,9 +36999,38 @@
         <v>56.2799987792969</v>
       </c>
       <c r="H1263" t="n">
-        <v>3316954</v>
+        <v>3398900</v>
       </c>
       <c r="I1263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1264" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>56.2999992370605</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>57.1534996032715</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>55.8499984741211</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>56.6500015258789</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>56.6500015258789</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>3324523</v>
+      </c>
+      <c r="I1264" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -37013,10 +37013,10 @@
         <v>46321.5625</v>
       </c>
       <c r="C1264" t="n">
-        <v>56.2999992370605</v>
+        <v>56.4000015258789</v>
       </c>
       <c r="D1264" t="n">
-        <v>57.1534996032715</v>
+        <v>57.1539993286133</v>
       </c>
       <c r="E1264" t="n">
         <v>55.8499984741211</v>
@@ -37028,9 +37028,38 @@
         <v>56.6500015258789</v>
       </c>
       <c r="H1264" t="n">
-        <v>3324523</v>
+        <v>3324800</v>
       </c>
       <c r="I1264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1265" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>56</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>57.2200012207031</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>55.6699981689453</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>56.8199996948242</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>56.8199996948242</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>1809993</v>
+      </c>
+      <c r="I1265" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -37057,9 +37057,38 @@
         <v>56.8199996948242</v>
       </c>
       <c r="H1265" t="n">
-        <v>1809993</v>
+        <v>1810300</v>
       </c>
       <c r="I1265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1266" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1266" t="n">
+        <v>55.7719993591309</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>58.0099983215332</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>55.7719993591309</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>57.9700012207031</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>57.9700012207031</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>2824967</v>
+      </c>
+      <c r="I1266" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -37071,7 +37071,7 @@
         <v>46323.5625</v>
       </c>
       <c r="C1266" t="n">
-        <v>55.7719993591309</v>
+        <v>56.1800003051758</v>
       </c>
       <c r="D1266" t="n">
         <v>58.0099983215332</v>
@@ -37086,9 +37086,38 @@
         <v>57.9700012207031</v>
       </c>
       <c r="H1266" t="n">
-        <v>2824967</v>
+        <v>2835200</v>
       </c>
       <c r="I1266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1267" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1267" t="n">
+        <v>55.0299987792969</v>
+      </c>
+      <c r="D1267" t="n">
+        <v>57.5499992370605</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>54.3499984741211</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>56.6500015258789</v>
+      </c>
+      <c r="G1267" t="n">
+        <v>56.6500015258789</v>
+      </c>
+      <c r="H1267" t="n">
+        <v>2158687</v>
+      </c>
+      <c r="I1267" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GTLB.xlsx
+++ b/data/GTLB.xlsx
@@ -37115,9 +37115,38 @@
         <v>56.6500015258789</v>
       </c>
       <c r="H1267" t="n">
-        <v>2158687</v>
+        <v>2159300</v>
       </c>
       <c r="I1267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1268" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1268" t="n">
+        <v>55.560001373291</v>
+      </c>
+      <c r="D1268" t="n">
+        <v>56.4500007629395</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>54.0900001525879</v>
+      </c>
+      <c r="G1268" t="n">
+        <v>54.0900001525879</v>
+      </c>
+      <c r="H1268" t="n">
+        <v>3207228</v>
+      </c>
+      <c r="I1268" t="s">
         <v>9</v>
       </c>
     </row>
